--- a/docs/HymnLink_data.xlsx
+++ b/docs/HymnLink_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sywan/My Drive (sxw154@gmail.com)/_Sync/Hymnals/HymnLink/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8111C94-C566-3E40-A801-9C95F55CAFCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A95F3830-73E9-F84B-9040-A2460FFE865F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-56500" yWindow="-2680" windowWidth="38920" windowHeight="25520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20820" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hymns" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5635" uniqueCount="3020">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5647" uniqueCount="3027">
   <si>
     <t>id</t>
   </si>
@@ -9052,16 +9052,7 @@
     <t>admin</t>
   </si>
   <si>
-    <t>系統管理員</t>
-  </si>
-  <si>
-    <t>test@gmail.com</t>
-  </si>
-  <si>
     <t>user</t>
-  </si>
-  <si>
-    <t>一般使用者</t>
   </si>
   <si>
     <t>timestamp</t>
@@ -9218,6 +9209,36 @@
   </si>
   <si>
     <t>石磐音樂</t>
+  </si>
+  <si>
+    <t>sywan@gap.cgu.edu.tw</t>
+  </si>
+  <si>
+    <t>fishandsalthiking@gmail.com</t>
+  </si>
+  <si>
+    <t>infotechtutor.4o@gmail.com</t>
+  </si>
+  <si>
+    <t>gamer.wan101@gmail.com</t>
+  </si>
+  <si>
+    <t>Shu-Yen Wan</t>
+  </si>
+  <si>
+    <t>Fish and Salt Hiking</t>
+  </si>
+  <si>
+    <t>InfoTech Tutor for ALL</t>
+  </si>
+  <si>
+    <t>Gamer</t>
+  </si>
+  <si>
+    <t>CGU AACSB</t>
+  </si>
+  <si>
+    <t>sxw154@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -9703,16 +9724,16 @@
         <v>21</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>3008</v>
+        <v>3005</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>3009</v>
+        <v>3006</v>
       </c>
       <c r="J2" t="s">
-        <v>3006</v>
+        <v>3003</v>
       </c>
       <c r="K2" t="s">
-        <v>3006</v>
+        <v>3003</v>
       </c>
       <c r="L2" t="s">
         <v>22</v>
@@ -9721,7 +9742,7 @@
         <v>23</v>
       </c>
       <c r="N2" t="s">
-        <v>3007</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.25">
@@ -9732,7 +9753,7 @@
         <v>25</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>3010</v>
+        <v>3007</v>
       </c>
       <c r="D3" t="s">
         <v>26</v>
@@ -9741,10 +9762,10 @@
         <v>27</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>3011</v>
+        <v>3008</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>3013</v>
+        <v>3010</v>
       </c>
       <c r="J3" t="s">
         <v>28</v>
@@ -9788,10 +9809,10 @@
         <v>27</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>3014</v>
+        <v>3011</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>3012</v>
+        <v>3009</v>
       </c>
       <c r="J4" t="s">
         <v>28</v>
@@ -9856,28 +9877,28 @@
         <v>27</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>3012</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>3013</v>
+      </c>
+      <c r="J6" t="s">
+        <v>3014</v>
+      </c>
+      <c r="K6" t="s">
+        <v>3014</v>
+      </c>
+      <c r="L6" t="s">
         <v>3015</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
         <v>3016</v>
       </c>
-      <c r="J6" t="s">
-        <v>3017</v>
-      </c>
-      <c r="K6" t="s">
-        <v>3017</v>
-      </c>
-      <c r="L6" t="s">
-        <v>3018</v>
-      </c>
-      <c r="M6" t="s">
-        <v>23</v>
-      </c>
-      <c r="N6" t="s">
-        <v>3019</v>
-      </c>
       <c r="P6" t="s">
-        <v>3019</v>
+        <v>3016</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="16" customHeight="1" x14ac:dyDescent="0.25">
@@ -11794,7 +11815,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>403</v>
       </c>
@@ -11838,7 +11859,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>411</v>
       </c>
@@ -11882,7 +11903,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="65" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>418</v>
       </c>
@@ -11970,7 +11991,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>429</v>
       </c>
@@ -12058,7 +12079,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="69" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>445</v>
       </c>
@@ -12146,7 +12167,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="71" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>457</v>
       </c>
@@ -12332,7 +12353,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>484</v>
       </c>
@@ -12355,7 +12376,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>489</v>
       </c>
@@ -12399,7 +12420,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>495</v>
       </c>
@@ -12443,7 +12464,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="32" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:17" ht="48" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>500</v>
       </c>
@@ -12508,7 +12529,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:17" ht="48" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>509</v>
       </c>
@@ -12640,7 +12661,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="32" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:17" ht="48" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>531</v>
       </c>
@@ -12684,7 +12705,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="86" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>536</v>
       </c>
@@ -12710,7 +12731,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="87" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>541</v>
       </c>
@@ -12730,7 +12751,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>545</v>
       </c>
@@ -12756,7 +12777,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="89" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>549</v>
       </c>
@@ -12800,7 +12821,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="90" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>554</v>
       </c>
@@ -12852,7 +12873,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>563</v>
       </c>
@@ -12878,7 +12899,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>567</v>
       </c>
@@ -12924,7 +12945,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="95" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>576</v>
       </c>
@@ -12950,7 +12971,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>580</v>
       </c>
@@ -13040,7 +13061,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="99" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>594</v>
       </c>
@@ -13128,7 +13149,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>607</v>
       </c>
@@ -13180,7 +13201,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>615</v>
       </c>
@@ -13224,7 +13245,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>620</v>
       </c>
@@ -13250,7 +13271,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>625</v>
       </c>
@@ -13270,7 +13291,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="32" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:17" ht="48" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>629</v>
       </c>
@@ -13406,7 +13427,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="111" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>652</v>
       </c>
@@ -13458,7 +13479,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="113" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>663</v>
       </c>
@@ -13536,7 +13557,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="116" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>675</v>
       </c>
@@ -13562,7 +13583,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>679</v>
       </c>
@@ -13658,7 +13679,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>694</v>
       </c>
@@ -13704,7 +13725,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="122" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>702</v>
       </c>
@@ -13961,7 +13982,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="132" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
         <v>751</v>
       </c>
@@ -14613,7 +14634,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="155" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
         <v>869</v>
       </c>
@@ -14648,7 +14669,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="156" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>875</v>
       </c>
@@ -14674,7 +14695,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="157" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>880</v>
       </c>
@@ -14700,7 +14721,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="158" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>885</v>
       </c>
@@ -14848,7 +14869,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="163" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
         <v>912</v>
       </c>
@@ -14892,7 +14913,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="164" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
         <v>913</v>
       </c>
@@ -15039,7 +15060,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="170" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
         <v>940</v>
       </c>
@@ -15143,7 +15164,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
         <v>959</v>
       </c>
@@ -15189,7 +15210,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="176" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
         <v>967</v>
       </c>
@@ -15212,7 +15233,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="177" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
         <v>970</v>
       </c>
@@ -15238,7 +15259,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="178" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
         <v>974</v>
       </c>
@@ -15264,7 +15285,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="179" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
         <v>978</v>
       </c>
@@ -15316,7 +15337,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="181" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
         <v>988</v>
       </c>
@@ -15553,7 +15574,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
         <v>1035</v>
       </c>
@@ -15706,7 +15727,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="196" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>1065</v>
       </c>
@@ -15726,7 +15747,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>1069</v>
       </c>
@@ -15873,7 +15894,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="203" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>1095</v>
       </c>
@@ -16377,7 +16398,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="224" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>1188</v>
       </c>
@@ -16397,7 +16418,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="225" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>1192</v>
       </c>
@@ -16461,7 +16482,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="227" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>1205</v>
       </c>
@@ -16551,7 +16572,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="230" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>1220</v>
       </c>
@@ -16597,7 +16618,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="232" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>1229</v>
       </c>
@@ -16623,7 +16644,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="233" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>1235</v>
       </c>
@@ -16649,7 +16670,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="234" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>1240</v>
       </c>
@@ -16797,7 +16818,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="239" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>1264</v>
       </c>
@@ -16823,7 +16844,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="240" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>1269</v>
       </c>
@@ -16849,7 +16870,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="241" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>1274</v>
       </c>
@@ -17700,7 +17721,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="275" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>1435</v>
       </c>
@@ -17749,7 +17770,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="277" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>1443</v>
       </c>
@@ -17769,7 +17790,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="278" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>1447</v>
       </c>
@@ -17859,7 +17880,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="281" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>1458</v>
       </c>
@@ -18003,7 +18024,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="287" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>1486</v>
       </c>
@@ -18107,7 +18128,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="291" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>1507</v>
       </c>
@@ -18185,7 +18206,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="294" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>1519</v>
       </c>
@@ -18211,7 +18232,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="295" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>1524</v>
       </c>
@@ -18237,7 +18258,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="296" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>1528</v>
       </c>
@@ -18263,7 +18284,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="297" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>1532</v>
       </c>
@@ -18338,7 +18359,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="300" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>1547</v>
       </c>
@@ -18382,7 +18403,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="301" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>1554</v>
       </c>
@@ -18560,7 +18581,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="306" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>1582</v>
       </c>
@@ -18648,7 +18669,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="308" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>1595</v>
       </c>
@@ -18780,7 +18801,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="311" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>1611</v>
       </c>
@@ -18956,7 +18977,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="315" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>1628</v>
       </c>
@@ -19044,7 +19065,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="317" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>1639</v>
       </c>
@@ -19132,7 +19153,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="319" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>1650</v>
       </c>
@@ -19352,7 +19373,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="324" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
         <v>1678</v>
       </c>
@@ -19378,7 +19399,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="325" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
         <v>1684</v>
       </c>
@@ -19636,7 +19657,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="331" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
         <v>1717</v>
       </c>
@@ -19724,7 +19745,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="333" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
         <v>1730</v>
       </c>
@@ -19973,7 +19994,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="342" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
         <v>1775</v>
       </c>
@@ -20071,7 +20092,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="346" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
         <v>1794</v>
       </c>
@@ -20159,7 +20180,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="348" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
         <v>1803</v>
       </c>
@@ -20291,7 +20312,7 @@
         <v>1817</v>
       </c>
     </row>
-    <row r="351" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
         <v>1818</v>
       </c>
@@ -20379,7 +20400,7 @@
         <v>1827</v>
       </c>
     </row>
-    <row r="353" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
         <v>1828</v>
       </c>
@@ -20467,7 +20488,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="355" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
         <v>1839</v>
       </c>
@@ -20725,7 +20746,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="361" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
         <v>1874</v>
       </c>
@@ -20813,7 +20834,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="363" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
         <v>1889</v>
       </c>
@@ -20857,7 +20878,7 @@
         <v>1894</v>
       </c>
     </row>
-    <row r="364" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
         <v>1895</v>
       </c>
@@ -20924,7 +20945,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="366" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
         <v>1905</v>
       </c>
@@ -20968,7 +20989,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="367" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
         <v>1911</v>
       </c>
@@ -21012,7 +21033,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="368" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
         <v>1916</v>
       </c>
@@ -21144,7 +21165,7 @@
         <v>1932</v>
       </c>
     </row>
-    <row r="371" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
         <v>1933</v>
       </c>
@@ -21232,7 +21253,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="373" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
         <v>1943</v>
       </c>
@@ -21276,7 +21297,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="374" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>1948</v>
       </c>
@@ -21320,7 +21341,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="375" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>1955</v>
       </c>
@@ -21364,7 +21385,7 @@
         <v>1959</v>
       </c>
     </row>
-    <row r="376" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="376" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
         <v>1960</v>
       </c>
@@ -21408,7 +21429,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="377" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
         <v>1965</v>
       </c>
@@ -21452,7 +21473,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="378" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
         <v>1972</v>
       </c>
@@ -21540,7 +21561,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="380" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
         <v>1979</v>
       </c>
@@ -21584,7 +21605,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="381" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="381" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
         <v>1986</v>
       </c>
@@ -21628,7 +21649,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="382" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
         <v>1991</v>
       </c>
@@ -21760,7 +21781,7 @@
         <v>2006</v>
       </c>
     </row>
-    <row r="385" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
         <v>2007</v>
       </c>
@@ -21892,7 +21913,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="388" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>2025</v>
       </c>
@@ -21936,7 +21957,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="389" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>2031</v>
       </c>
@@ -21980,7 +22001,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="390" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>2036</v>
       </c>
@@ -22068,7 +22089,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="392" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>2048</v>
       </c>
@@ -22112,7 +22133,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="393" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>2053</v>
       </c>
@@ -22270,7 +22291,7 @@
         <v>2074</v>
       </c>
     </row>
-    <row r="397" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>2075</v>
       </c>
@@ -22314,7 +22335,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="398" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>2080</v>
       </c>
@@ -22428,7 +22449,7 @@
         <v>2095</v>
       </c>
     </row>
-    <row r="401" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>2096</v>
       </c>
@@ -22498,7 +22519,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="403" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>2107</v>
       </c>
@@ -22542,7 +22563,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="404" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>2112</v>
       </c>
@@ -22586,7 +22607,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="405" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>2114</v>
       </c>
@@ -22630,7 +22651,7 @@
         <v>2118</v>
       </c>
     </row>
-    <row r="406" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>2119</v>
       </c>
@@ -22674,7 +22695,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="407" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>2125</v>
       </c>
@@ -22700,7 +22721,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="408" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>2131</v>
       </c>
@@ -22860,7 +22881,7 @@
         <v>2153</v>
       </c>
     </row>
-    <row r="413" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>2154</v>
       </c>
@@ -22968,7 +22989,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="416" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>2168</v>
       </c>
@@ -23012,7 +23033,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="417" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>2173</v>
       </c>
@@ -23038,7 +23059,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="418" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>2179</v>
       </c>
@@ -23214,7 +23235,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="422" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>2202</v>
       </c>
@@ -23307,7 +23328,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="425" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>2217</v>
       </c>
@@ -23405,7 +23426,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="429" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>2236</v>
       </c>
@@ -23529,7 +23550,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="434" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>2263</v>
       </c>
@@ -23575,7 +23596,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="436" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>2271</v>
       </c>
@@ -23687,7 +23708,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="441" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>2292</v>
       </c>
@@ -23757,7 +23778,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="443" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>2302</v>
       </c>
@@ -23809,7 +23830,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="445" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>2313</v>
       </c>
@@ -24100,7 +24121,7 @@
         <v>2353</v>
       </c>
     </row>
-    <row r="454" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
         <v>2354</v>
       </c>
@@ -24144,7 +24165,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="455" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
         <v>2360</v>
       </c>
@@ -24188,7 +24209,7 @@
         <v>2365</v>
       </c>
     </row>
-    <row r="456" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A456" t="s">
         <v>2366</v>
       </c>
@@ -24208,7 +24229,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="457" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A457" t="s">
         <v>2368</v>
       </c>
@@ -24277,7 +24298,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="460" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
         <v>2380</v>
       </c>
@@ -24297,7 +24318,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="461" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
         <v>2383</v>
       </c>
@@ -24387,7 +24408,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="464" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A464" t="s">
         <v>2397</v>
       </c>
@@ -24407,7 +24428,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="465" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
         <v>2401</v>
       </c>
@@ -24427,7 +24448,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="466" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A466" t="s">
         <v>2405</v>
       </c>
@@ -24569,7 +24590,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="471" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A471" t="s">
         <v>2425</v>
       </c>
@@ -24595,7 +24616,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="472" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A472" t="s">
         <v>2431</v>
       </c>
@@ -24731,7 +24752,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="477" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>2458</v>
       </c>
@@ -24832,7 +24853,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="481" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>2475</v>
       </c>
@@ -24910,7 +24931,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="484" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>2491</v>
       </c>
@@ -24936,7 +24957,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="485" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>2495</v>
       </c>
@@ -25089,7 +25110,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="491" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>2524</v>
       </c>
@@ -25193,7 +25214,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="495" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>2540</v>
       </c>
@@ -25245,7 +25266,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="497" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>2550</v>
       </c>
@@ -25502,7 +25523,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="507" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A507" t="s">
         <v>2597</v>
       </c>
@@ -25528,7 +25549,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="508" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A508" t="s">
         <v>2601</v>
       </c>
@@ -25574,7 +25595,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="510" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A510" t="s">
         <v>2611</v>
       </c>
@@ -25692,7 +25713,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="515" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A515" t="s">
         <v>2633</v>
       </c>
@@ -26229,7 +26250,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="536" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A536" t="s">
         <v>2727</v>
       </c>
@@ -26255,7 +26276,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="537" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="537" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A537" t="s">
         <v>2732</v>
       </c>
@@ -26353,7 +26374,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="541" spans="1:17" ht="16" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:17" ht="32" x14ac:dyDescent="0.2">
       <c r="A541" t="s">
         <v>2750</v>
       </c>
@@ -26497,7 +26518,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="547" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A547" t="s">
         <v>2777</v>
       </c>
@@ -26563,7 +26584,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="550" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A550" t="s">
         <v>2790</v>
       </c>
@@ -26771,7 +26792,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="558" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A558" t="s">
         <v>2828</v>
       </c>
@@ -26797,7 +26818,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="559" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="559" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A559" t="s">
         <v>2833</v>
       </c>
@@ -26823,7 +26844,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="560" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="560" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A560" t="s">
         <v>2836</v>
       </c>
@@ -26875,7 +26896,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="562" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A562" t="s">
         <v>2844</v>
       </c>
@@ -26927,7 +26948,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="564" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="564" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A564" t="s">
         <v>2854</v>
       </c>
@@ -26999,7 +27020,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="567" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A567" t="s">
         <v>2867</v>
       </c>
@@ -27025,7 +27046,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="568" spans="1:13" ht="16" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:13" ht="32" x14ac:dyDescent="0.2">
       <c r="A568" t="s">
         <v>2872</v>
       </c>
@@ -27143,7 +27164,7 @@
         <v>21</v>
       </c>
       <c r="G572" s="4" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="M572" t="s">
         <v>23</v>
@@ -27186,7 +27207,7 @@
         <v>570</v>
       </c>
       <c r="G574" s="4" t="s">
-        <v>2998</v>
+        <v>2995</v>
       </c>
       <c r="L574" t="s">
         <v>2900</v>
@@ -27515,37 +27536,37 @@
         <v>2958</v>
       </c>
       <c r="C587" t="s">
+        <v>2999</v>
+      </c>
+      <c r="D587" t="s">
+        <v>2998</v>
+      </c>
+      <c r="E587" t="s">
+        <v>21</v>
+      </c>
+      <c r="F587" t="s">
+        <v>2996</v>
+      </c>
+      <c r="G587" s="4" t="s">
+        <v>2997</v>
+      </c>
+      <c r="J587" t="s">
+        <v>3000</v>
+      </c>
+      <c r="K587" t="s">
+        <v>3000</v>
+      </c>
+      <c r="L587" t="s">
+        <v>3001</v>
+      </c>
+      <c r="M587" t="s">
+        <v>23</v>
+      </c>
+      <c r="N587" t="s">
         <v>3002</v>
       </c>
-      <c r="D587" t="s">
-        <v>3001</v>
-      </c>
-      <c r="E587" t="s">
-        <v>21</v>
-      </c>
-      <c r="F587" t="s">
-        <v>2999</v>
-      </c>
-      <c r="G587" s="4" t="s">
-        <v>3000</v>
-      </c>
-      <c r="J587" t="s">
-        <v>3003</v>
-      </c>
-      <c r="K587" t="s">
-        <v>3003</v>
-      </c>
-      <c r="L587" t="s">
-        <v>3004</v>
-      </c>
-      <c r="M587" t="s">
-        <v>23</v>
-      </c>
-      <c r="N587" t="s">
-        <v>3005</v>
-      </c>
       <c r="P587" t="s">
-        <v>3005</v>
+        <v>3002</v>
       </c>
     </row>
   </sheetData>
@@ -27724,12 +27745,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="89.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="89.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -27751,23 +27772,71 @@
         <v>2984</v>
       </c>
       <c r="C2" t="s">
-        <v>2985</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>2986</v>
+        <v>3017</v>
       </c>
       <c r="B3" t="s">
-        <v>2987</v>
+        <v>2985</v>
       </c>
       <c r="C3" t="s">
-        <v>2988</v>
+        <v>3021</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>3018</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3022</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>3019</v>
+      </c>
+      <c r="B5" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3023</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>3020</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>3026</v>
+      </c>
+      <c r="B7" t="s">
+        <v>2984</v>
+      </c>
+      <c r="C7" t="s">
+        <v>3021</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="A4" r:id="rId2" xr:uid="{30139D6C-3070-6D4F-A11B-903D83402028}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{F0FF30ED-B55E-1A4A-8F35-64BCCE04526D}"/>
+    <hyperlink ref="A6" r:id="rId4" xr:uid="{48B579D1-A849-764B-84CE-2180A547C8F4}"/>
+    <hyperlink ref="A7" r:id="rId5" xr:uid="{1100E7E6-CA38-B347-9962-12FA22D6D32C}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -27789,30 +27858,30 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>2986</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2987</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2988</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2989</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2990</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2991</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2992</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2993</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>2994</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2995</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>2996</v>
+        <v>2993</v>
       </c>
     </row>
   </sheetData>
